--- a/Assets/Assets/Tables/棋盘系统表.xlsx
+++ b/Assets/Assets/Tables/棋盘系统表.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KIM\Pin\XX\配表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\unity\unity文件\聚光灯\shangdi\Assets\Assets\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8E2D60-6A49-4C77-82BF-AE85297AE5DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="23215" windowHeight="9829" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="棋盘表" sheetId="1" r:id="rId1"/>
@@ -20,7 +19,20 @@
     <sheet name="刷新区域表" sheetId="5" r:id="rId5"/>
     <sheet name="刷新区域_元素权重" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -327,13 +339,19 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -348,14 +366,158 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -365,15 +527,203 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E1F2"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -396,9 +746,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -415,17 +1007,61 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -710,14 +1346,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -725,7 +1361,7 @@
     <col min="5" max="5" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -742,7 +1378,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -759,7 +1395,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -776,7 +1412,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="4" ht="30.05" spans="1:5">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -794,15 +1430,16 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -811,7 +1448,7 @@
     <col min="5" max="5" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
@@ -828,7 +1465,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>18</v>
       </c>
@@ -845,7 +1482,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -862,7 +1499,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="4" ht="30.05" spans="1:5">
       <c r="A4" s="3">
         <v>0</v>
       </c>
@@ -879,7 +1516,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" ht="15.05" spans="1:5">
       <c r="A5" s="3">
         <v>1</v>
       </c>
@@ -896,7 +1533,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="6" ht="30.05" spans="1:5">
       <c r="A6" s="3">
         <v>2</v>
       </c>
@@ -914,15 +1551,16 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E103"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="3" width="8" customWidth="1"/>
@@ -930,7 +1568,7 @@
     <col min="5" max="5" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -947,7 +1585,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -964,7 +1602,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -981,7 +1619,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -996,7 +1634,7 @@
       </c>
       <c r="E4" s="4"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5" s="3">
         <v>1</v>
       </c>
@@ -1011,7 +1649,7 @@
       </c>
       <c r="E5" s="4"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -1026,7 +1664,7 @@
       </c>
       <c r="E6" s="4"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5">
       <c r="A7" s="3">
         <v>1</v>
       </c>
@@ -1041,7 +1679,7 @@
       </c>
       <c r="E7" s="4"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5">
       <c r="A8" s="3">
         <v>1</v>
       </c>
@@ -1056,7 +1694,7 @@
       </c>
       <c r="E8" s="4"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5">
       <c r="A9" s="3">
         <v>1</v>
       </c>
@@ -1071,7 +1709,7 @@
       </c>
       <c r="E9" s="4"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5">
       <c r="A10" s="3">
         <v>1</v>
       </c>
@@ -1086,7 +1724,7 @@
       </c>
       <c r="E10" s="4"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5">
       <c r="A11" s="3">
         <v>1</v>
       </c>
@@ -1101,7 +1739,7 @@
       </c>
       <c r="E11" s="4"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5">
       <c r="A12" s="3">
         <v>1</v>
       </c>
@@ -1116,7 +1754,7 @@
       </c>
       <c r="E12" s="4"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5">
       <c r="A13" s="3">
         <v>1</v>
       </c>
@@ -1131,7 +1769,7 @@
       </c>
       <c r="E13" s="4"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5">
       <c r="A14" s="3">
         <v>1</v>
       </c>
@@ -1146,7 +1784,7 @@
       </c>
       <c r="E14" s="4"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5">
       <c r="A15" s="3">
         <v>1</v>
       </c>
@@ -1161,7 +1799,7 @@
       </c>
       <c r="E15" s="4"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5">
       <c r="A16" s="3">
         <v>1</v>
       </c>
@@ -1176,7 +1814,7 @@
       </c>
       <c r="E16" s="4"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5">
       <c r="A17" s="3">
         <v>1</v>
       </c>
@@ -1191,7 +1829,7 @@
       </c>
       <c r="E17" s="4"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5">
       <c r="A18" s="3">
         <v>1</v>
       </c>
@@ -1206,7 +1844,7 @@
       </c>
       <c r="E18" s="4"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5">
       <c r="A19" s="3">
         <v>1</v>
       </c>
@@ -1221,7 +1859,7 @@
       </c>
       <c r="E19" s="4"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5">
       <c r="A20" s="3">
         <v>1</v>
       </c>
@@ -1236,7 +1874,7 @@
       </c>
       <c r="E20" s="4"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5">
       <c r="A21" s="3">
         <v>1</v>
       </c>
@@ -1251,7 +1889,7 @@
       </c>
       <c r="E21" s="4"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5">
       <c r="A22" s="3">
         <v>1</v>
       </c>
@@ -1266,7 +1904,7 @@
       </c>
       <c r="E22" s="4"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5">
       <c r="A23" s="3">
         <v>1</v>
       </c>
@@ -1281,7 +1919,7 @@
       </c>
       <c r="E23" s="4"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5">
       <c r="A24" s="3">
         <v>1</v>
       </c>
@@ -1296,7 +1934,7 @@
       </c>
       <c r="E24" s="4"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5">
       <c r="A25" s="3">
         <v>1</v>
       </c>
@@ -1311,7 +1949,7 @@
       </c>
       <c r="E25" s="4"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5">
       <c r="A26" s="3">
         <v>1</v>
       </c>
@@ -1326,7 +1964,7 @@
       </c>
       <c r="E26" s="4"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5">
       <c r="A27" s="3">
         <v>1</v>
       </c>
@@ -1341,7 +1979,7 @@
       </c>
       <c r="E27" s="4"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5">
       <c r="A28" s="3">
         <v>1</v>
       </c>
@@ -1356,7 +1994,7 @@
       </c>
       <c r="E28" s="4"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5">
       <c r="A29" s="3">
         <v>1</v>
       </c>
@@ -1371,7 +2009,7 @@
       </c>
       <c r="E29" s="4"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5">
       <c r="A30" s="3">
         <v>1</v>
       </c>
@@ -1386,7 +2024,7 @@
       </c>
       <c r="E30" s="4"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5">
       <c r="A31" s="3">
         <v>1</v>
       </c>
@@ -1401,7 +2039,7 @@
       </c>
       <c r="E31" s="4"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5">
       <c r="A32" s="3">
         <v>1</v>
       </c>
@@ -1416,7 +2054,7 @@
       </c>
       <c r="E32" s="4"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5">
       <c r="A33" s="3">
         <v>1</v>
       </c>
@@ -1431,7 +2069,7 @@
       </c>
       <c r="E33" s="4"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5">
       <c r="A34" s="3">
         <v>1</v>
       </c>
@@ -1446,7 +2084,7 @@
       </c>
       <c r="E34" s="4"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5">
       <c r="A35" s="3">
         <v>1</v>
       </c>
@@ -1461,7 +2099,7 @@
       </c>
       <c r="E35" s="4"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5">
       <c r="A36" s="3">
         <v>1</v>
       </c>
@@ -1476,7 +2114,7 @@
       </c>
       <c r="E36" s="4"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5">
       <c r="A37" s="3">
         <v>1</v>
       </c>
@@ -1491,7 +2129,7 @@
       </c>
       <c r="E37" s="4"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5">
       <c r="A38" s="3">
         <v>1</v>
       </c>
@@ -1506,7 +2144,7 @@
       </c>
       <c r="E38" s="4"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5">
       <c r="A39" s="3">
         <v>1</v>
       </c>
@@ -1521,7 +2159,7 @@
       </c>
       <c r="E39" s="4"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5">
       <c r="A40" s="3">
         <v>1</v>
       </c>
@@ -1536,7 +2174,7 @@
       </c>
       <c r="E40" s="4"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5">
       <c r="A41" s="3">
         <v>1</v>
       </c>
@@ -1551,7 +2189,7 @@
       </c>
       <c r="E41" s="4"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5">
       <c r="A42" s="3">
         <v>1</v>
       </c>
@@ -1566,7 +2204,7 @@
       </c>
       <c r="E42" s="4"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5">
       <c r="A43" s="3">
         <v>1</v>
       </c>
@@ -1581,7 +2219,7 @@
       </c>
       <c r="E43" s="4"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5">
       <c r="A44" s="3">
         <v>1</v>
       </c>
@@ -1596,7 +2234,7 @@
       </c>
       <c r="E44" s="4"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5">
       <c r="A45" s="3">
         <v>1</v>
       </c>
@@ -1611,7 +2249,7 @@
       </c>
       <c r="E45" s="4"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5">
       <c r="A46" s="3">
         <v>1</v>
       </c>
@@ -1626,7 +2264,7 @@
       </c>
       <c r="E46" s="4"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5">
       <c r="A47" s="3">
         <v>1</v>
       </c>
@@ -1641,7 +2279,7 @@
       </c>
       <c r="E47" s="4"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5">
       <c r="A48" s="3">
         <v>1</v>
       </c>
@@ -1656,7 +2294,7 @@
       </c>
       <c r="E48" s="4"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5">
       <c r="A49" s="3">
         <v>1</v>
       </c>
@@ -1671,7 +2309,7 @@
       </c>
       <c r="E49" s="4"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5">
       <c r="A50" s="3">
         <v>1</v>
       </c>
@@ -1686,7 +2324,7 @@
       </c>
       <c r="E50" s="4"/>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5">
       <c r="A51" s="3">
         <v>1</v>
       </c>
@@ -1701,7 +2339,7 @@
       </c>
       <c r="E51" s="4"/>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5">
       <c r="A52" s="3">
         <v>1</v>
       </c>
@@ -1716,7 +2354,7 @@
       </c>
       <c r="E52" s="4"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5">
       <c r="A53" s="3">
         <v>1</v>
       </c>
@@ -1731,7 +2369,7 @@
       </c>
       <c r="E53" s="4"/>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5">
       <c r="A54" s="3">
         <v>1</v>
       </c>
@@ -1746,7 +2384,7 @@
       </c>
       <c r="E54" s="4"/>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5">
       <c r="A55" s="3">
         <v>1</v>
       </c>
@@ -1761,7 +2399,7 @@
       </c>
       <c r="E55" s="4"/>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5">
       <c r="A56" s="3">
         <v>1</v>
       </c>
@@ -1776,7 +2414,7 @@
       </c>
       <c r="E56" s="4"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5">
       <c r="A57" s="3">
         <v>1</v>
       </c>
@@ -1791,7 +2429,7 @@
       </c>
       <c r="E57" s="4"/>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5">
       <c r="A58" s="3">
         <v>1</v>
       </c>
@@ -1806,7 +2444,7 @@
       </c>
       <c r="E58" s="4"/>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5">
       <c r="A59" s="3">
         <v>1</v>
       </c>
@@ -1821,7 +2459,7 @@
       </c>
       <c r="E59" s="4"/>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5">
       <c r="A60" s="3">
         <v>1</v>
       </c>
@@ -1836,7 +2474,7 @@
       </c>
       <c r="E60" s="4"/>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5">
       <c r="A61" s="3">
         <v>1</v>
       </c>
@@ -1851,7 +2489,7 @@
       </c>
       <c r="E61" s="4"/>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5">
       <c r="A62" s="3">
         <v>1</v>
       </c>
@@ -1866,7 +2504,7 @@
       </c>
       <c r="E62" s="4"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5">
       <c r="A63" s="3">
         <v>1</v>
       </c>
@@ -1881,7 +2519,7 @@
       </c>
       <c r="E63" s="4"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5">
       <c r="A64" s="3">
         <v>1</v>
       </c>
@@ -1896,7 +2534,7 @@
       </c>
       <c r="E64" s="4"/>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5">
       <c r="A65" s="3">
         <v>1</v>
       </c>
@@ -1911,7 +2549,7 @@
       </c>
       <c r="E65" s="4"/>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5">
       <c r="A66" s="3">
         <v>1</v>
       </c>
@@ -1926,7 +2564,7 @@
       </c>
       <c r="E66" s="4"/>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5">
       <c r="A67" s="3">
         <v>1</v>
       </c>
@@ -1941,7 +2579,7 @@
       </c>
       <c r="E67" s="4"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5">
       <c r="A68" s="3">
         <v>1</v>
       </c>
@@ -1956,7 +2594,7 @@
       </c>
       <c r="E68" s="4"/>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5">
       <c r="A69" s="3">
         <v>1</v>
       </c>
@@ -1971,7 +2609,7 @@
       </c>
       <c r="E69" s="4"/>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5">
       <c r="A70" s="3">
         <v>1</v>
       </c>
@@ -1986,7 +2624,7 @@
       </c>
       <c r="E70" s="4"/>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5">
       <c r="A71" s="3">
         <v>1</v>
       </c>
@@ -2001,7 +2639,7 @@
       </c>
       <c r="E71" s="4"/>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5">
       <c r="A72" s="3">
         <v>1</v>
       </c>
@@ -2016,7 +2654,7 @@
       </c>
       <c r="E72" s="4"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5">
       <c r="A73" s="3">
         <v>1</v>
       </c>
@@ -2031,7 +2669,7 @@
       </c>
       <c r="E73" s="4"/>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5">
       <c r="A74" s="3">
         <v>1</v>
       </c>
@@ -2046,7 +2684,7 @@
       </c>
       <c r="E74" s="4"/>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5">
       <c r="A75" s="3">
         <v>1</v>
       </c>
@@ -2061,7 +2699,7 @@
       </c>
       <c r="E75" s="4"/>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5">
       <c r="A76" s="3">
         <v>1</v>
       </c>
@@ -2076,7 +2714,7 @@
       </c>
       <c r="E76" s="4"/>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5">
       <c r="A77" s="3">
         <v>1</v>
       </c>
@@ -2091,7 +2729,7 @@
       </c>
       <c r="E77" s="4"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5">
       <c r="A78" s="3">
         <v>1</v>
       </c>
@@ -2106,7 +2744,7 @@
       </c>
       <c r="E78" s="4"/>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5">
       <c r="A79" s="3">
         <v>1</v>
       </c>
@@ -2121,7 +2759,7 @@
       </c>
       <c r="E79" s="4"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5">
       <c r="A80" s="3">
         <v>1</v>
       </c>
@@ -2136,7 +2774,7 @@
       </c>
       <c r="E80" s="4"/>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5">
       <c r="A81" s="3">
         <v>1</v>
       </c>
@@ -2151,7 +2789,7 @@
       </c>
       <c r="E81" s="4"/>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5">
       <c r="A82" s="3">
         <v>1</v>
       </c>
@@ -2166,7 +2804,7 @@
       </c>
       <c r="E82" s="4"/>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5">
       <c r="A83" s="3">
         <v>1</v>
       </c>
@@ -2181,7 +2819,7 @@
       </c>
       <c r="E83" s="4"/>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5">
       <c r="A84" s="3">
         <v>1</v>
       </c>
@@ -2196,7 +2834,7 @@
       </c>
       <c r="E84" s="4"/>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5">
       <c r="A85" s="3">
         <v>1</v>
       </c>
@@ -2211,7 +2849,7 @@
       </c>
       <c r="E85" s="4"/>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5">
       <c r="A86" s="3">
         <v>1</v>
       </c>
@@ -2226,7 +2864,7 @@
       </c>
       <c r="E86" s="4"/>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5">
       <c r="A87" s="3">
         <v>1</v>
       </c>
@@ -2241,7 +2879,7 @@
       </c>
       <c r="E87" s="4"/>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5">
       <c r="A88" s="3">
         <v>1</v>
       </c>
@@ -2256,7 +2894,7 @@
       </c>
       <c r="E88" s="4"/>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5">
       <c r="A89" s="3">
         <v>1</v>
       </c>
@@ -2271,7 +2909,7 @@
       </c>
       <c r="E89" s="4"/>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5">
       <c r="A90" s="3">
         <v>1</v>
       </c>
@@ -2286,7 +2924,7 @@
       </c>
       <c r="E90" s="4"/>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5">
       <c r="A91" s="3">
         <v>1</v>
       </c>
@@ -2301,7 +2939,7 @@
       </c>
       <c r="E91" s="4"/>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5">
       <c r="A92" s="3">
         <v>1</v>
       </c>
@@ -2316,7 +2954,7 @@
       </c>
       <c r="E92" s="4"/>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5">
       <c r="A93" s="3">
         <v>1</v>
       </c>
@@ -2331,7 +2969,7 @@
       </c>
       <c r="E93" s="4"/>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5">
       <c r="A94" s="3">
         <v>1</v>
       </c>
@@ -2346,7 +2984,7 @@
       </c>
       <c r="E94" s="4"/>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5">
       <c r="A95" s="3">
         <v>1</v>
       </c>
@@ -2361,7 +2999,7 @@
       </c>
       <c r="E95" s="4"/>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5">
       <c r="A96" s="3">
         <v>1</v>
       </c>
@@ -2376,7 +3014,7 @@
       </c>
       <c r="E96" s="4"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5">
       <c r="A97" s="3">
         <v>1</v>
       </c>
@@ -2391,7 +3029,7 @@
       </c>
       <c r="E97" s="4"/>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5">
       <c r="A98" s="3">
         <v>1</v>
       </c>
@@ -2406,7 +3044,7 @@
       </c>
       <c r="E98" s="4"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5">
       <c r="A99" s="3">
         <v>1</v>
       </c>
@@ -2421,7 +3059,7 @@
       </c>
       <c r="E99" s="4"/>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5">
       <c r="A100" s="3">
         <v>1</v>
       </c>
@@ -2436,7 +3074,7 @@
       </c>
       <c r="E100" s="4"/>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5">
       <c r="A101" s="3">
         <v>1</v>
       </c>
@@ -2451,7 +3089,7 @@
       </c>
       <c r="E101" s="4"/>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5">
       <c r="A102" s="3">
         <v>1</v>
       </c>
@@ -2466,7 +3104,7 @@
       </c>
       <c r="E102" s="4"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5">
       <c r="A103" s="3">
         <v>1</v>
       </c>
@@ -2482,15 +3120,16 @@
       <c r="E103" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -2504,7 +3143,7 @@
     <col min="10" max="10" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>37</v>
       </c>
@@ -2536,7 +3175,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
         <v>45</v>
       </c>
@@ -2568,7 +3207,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -2600,7 +3239,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" ht="15.05" spans="1:10">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -2614,7 +3253,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="3">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F4" s="3">
         <v>8</v>
@@ -2632,7 +3271,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" ht="15.05" spans="1:10">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -2662,7 +3301,7 @@
       </c>
       <c r="J5" s="4"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" ht="15.05" spans="1:10">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -2694,7 +3333,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" ht="15.05" spans="1:10">
       <c r="A7" s="3">
         <v>4</v>
       </c>
@@ -2724,7 +3363,7 @@
       </c>
       <c r="J7" s="4"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" ht="15.05" spans="1:10">
       <c r="A8" s="3">
         <v>5</v>
       </c>
@@ -2755,15 +3394,16 @@
       <c r="J8" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
@@ -2772,7 +3412,7 @@
     <col min="10" max="10" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>66</v>
       </c>
@@ -2804,7 +3444,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
         <v>74</v>
       </c>
@@ -2836,7 +3476,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -2868,7 +3508,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" ht="15.05" spans="1:10">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -2898,7 +3538,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="5" ht="30.05" spans="1:10">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -2928,7 +3568,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" ht="15.05" spans="1:10">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -2958,7 +3598,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" ht="15.05" spans="1:10">
       <c r="A7" s="3">
         <v>4</v>
       </c>
@@ -2991,22 +3631,23 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>66</v>
       </c>
@@ -3020,7 +3661,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>74</v>
       </c>
@@ -3034,7 +3675,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -3048,7 +3689,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -3060,7 +3701,7 @@
       </c>
       <c r="D4" s="4"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" ht="15.05" spans="1:4">
       <c r="A5" s="3">
         <v>1</v>
       </c>
@@ -3074,7 +3715,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -3086,7 +3727,7 @@
       </c>
       <c r="D6" s="4"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4">
       <c r="A7" s="3">
         <v>1</v>
       </c>
@@ -3098,7 +3739,7 @@
       </c>
       <c r="D7" s="4"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4">
       <c r="A8" s="3">
         <v>2</v>
       </c>
@@ -3110,7 +3751,7 @@
       </c>
       <c r="D8" s="4"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" ht="15.05" spans="1:4">
       <c r="A9" s="3">
         <v>2</v>
       </c>
@@ -3124,7 +3765,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4">
       <c r="A10" s="3">
         <v>2</v>
       </c>
@@ -3136,7 +3777,7 @@
       </c>
       <c r="D10" s="4"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4">
       <c r="A11" s="3">
         <v>2</v>
       </c>
@@ -3148,7 +3789,7 @@
       </c>
       <c r="D11" s="4"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" ht="15.05" spans="1:4">
       <c r="A12" s="3">
         <v>3</v>
       </c>
@@ -3162,7 +3803,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4">
       <c r="A13" s="3">
         <v>3</v>
       </c>
@@ -3174,7 +3815,7 @@
       </c>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4">
       <c r="A14" s="3">
         <v>3</v>
       </c>
@@ -3186,7 +3827,7 @@
       </c>
       <c r="D14" s="4"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4">
       <c r="A15" s="3">
         <v>3</v>
       </c>
@@ -3198,7 +3839,7 @@
       </c>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4">
       <c r="A16" s="3">
         <v>4</v>
       </c>
@@ -3210,7 +3851,7 @@
       </c>
       <c r="D16" s="4"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" ht="15.05" spans="1:4">
       <c r="A17" s="3">
         <v>4</v>
       </c>
@@ -3224,7 +3865,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4">
       <c r="A18" s="3">
         <v>4</v>
       </c>
@@ -3236,7 +3877,7 @@
       </c>
       <c r="D18" s="4"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4">
       <c r="A19" s="3">
         <v>4</v>
       </c>
@@ -3249,7 +3890,7 @@
       <c r="D19" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>